--- a/projetos/excel/simulador-fundos-imobiliarios/simulador-fundos-imobiliarios.xlsx
+++ b/projetos/excel/simulador-fundos-imobiliarios/simulador-fundos-imobiliarios.xlsx
@@ -229,6 +229,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <pieChart>
@@ -242,9 +243,9 @@
             </a:ln>
           </spPr>
           <cat>
-            <numRef>
+            <strRef>
               <f>'Simulador'!$B$31:$B$36</f>
-            </numRef>
+            </strRef>
           </cat>
           <val>
             <numRef>
@@ -263,7 +264,8 @@
       </pieChart>
     </plotArea>
     <legend>
-      <legendPos val="r"/>
+      <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -280,7 +282,7 @@
       <row>5</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3960000" cy="2700000"/>
+    <ext cx="3960000" cy="3240000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
